--- a/src/Tests/Samples.DontScrub.Net4_8.verified.xlsx
+++ b/src/Tests/Samples.DontScrub.Net4_8.verified.xlsx
@@ -8,7 +8,7 @@
     <x:workbookView xWindow="10320" yWindow="4224" windowWidth="30960" windowHeight="12120" firstSheet="0" activeTab="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <x:sheet name="Sheet1" sheetId="1" r:id="DeterministicId5"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="191029"/>
